--- a/per-stock/CORZ/financials.xlsx
+++ b/per-stock/CORZ/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7696002560</v>
+        <v>9269534720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8846363648</v>
+        <v>10419896320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76.85714</v>
+        <v>98.29103000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.694893</v>
+        <v>26.130651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -715,11 +724,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>174972256</v>
+        <v>-461148000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -745,7 +754,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.21</v>
+        <v>29.16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -789,6 +798,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B54:E54)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B52:E52)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1896,13 +2376,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1912,6 +2392,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1922,30 +2403,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1958,21 +2444,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-124570000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>142169.87561</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-18950190</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-192255210</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>221003.667236</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-47221650</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1981,21 +2468,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.000443</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0.000356</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2004,21 +2492,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-10489000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-408858000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>54920000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>914867000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-646083000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-10010000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2027,21 +2516,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-311425000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>320623000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-90239000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-915501000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>621458000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-224865000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2050,21 +2540,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-311425000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>320623000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-90239000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-915501000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>621458000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-224865000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2073,21 +2564,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2096,21 +2588,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>19817000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>17115000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>19173000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>21484000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>22407000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>29155000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2119,21 +2612,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>85138000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>59008000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>77198000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>73603000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>71312000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>90162000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2142,21 +2636,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-321914000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-88235000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-35319000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-634000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-24625000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-234875000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2165,21 +2660,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-341731000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-105350000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-54492000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-22118000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-47032000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-264030000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2188,21 +2684,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-4857000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>821000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>1185000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>2187000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-1136000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2210,14 +2707,17 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>4857000</v>
+      </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n">
         <v>1136000</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>7072000</v>
       </c>
     </row>
@@ -2227,18 +2727,19 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>821000</v>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
         <v>2187000</v>
       </c>
-      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2247,21 +2748,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-160333000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-106330830.12439</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-72738190</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-213553210</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-44985996.332764</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-87897650</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2270,21 +2772,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2293,21 +2796,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>145540000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>185113000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>135595000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>100746000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>126557000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>134559000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2315,22 +2819,23 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="3" t="n">
+        <v>-310422000</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>-54792000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-26284000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-47038000</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>-39783000</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>-41219000</v>
-      </c>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2339,21 +2844,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>322911000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>464573000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>318562000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>317985000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>363314000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>306146000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2362,21 +2868,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>322911000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>319603000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>318562000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>317985000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>315186000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>306146000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2385,21 +2892,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-0.46</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2408,21 +2916,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-0.46</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>1.44</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2431,21 +2940,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-342438000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>180839000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-144876000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-13274000</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>576251000</v>
-      </c>
       <c r="F23" s="3" t="n">
-        <v>-265541000</v>
+        <v>448879000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2454,21 +2964,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-342438000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>180839000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-144876000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-13274000</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>576251000</v>
-      </c>
       <c r="F24" s="3" t="n">
-        <v>-265541000</v>
+        <v>448879000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2476,16 +2987,21 @@
           <t>Otherunder Preferred Stock Dividend</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n">
+      <c r="B25" s="3" t="n">
+        <v>-4750000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
         <v>849000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-923525000</v>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>127372000</v>
+      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2494,21 +3010,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2517,21 +3034,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2540,21 +3058,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2563,21 +3082,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>95000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>158000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>205000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>375000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2586,21 +3106,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-346588000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>214245000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-143902000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-936641000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>576456000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-265166000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2609,21 +3130,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-311435000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>320511000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-90231000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-915708000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>621301000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-224396000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2632,21 +3154,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-112000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-207000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-157000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>469000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2655,21 +3178,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-280626000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-9676000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-15375000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-5543000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-6000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-149000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2678,21 +3202,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-13638000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-2575000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-300000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-4166000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-6000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-149000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2701,21 +3226,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-4258000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>15075000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>1377000</v>
       </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n">
-        <v>673000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2727,10 +3253,11 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2740,16 +3267,21 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" s="3" t="n">
+        <v>266488000</v>
+      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n">
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2759,9 +3291,7 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
@@ -2774,7 +3304,10 @@
       <c r="F38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2783,21 +3316,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-30799000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>330299000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-74864000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-909958000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>621464000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-224716000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2806,21 +3340,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-4857000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>821000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1185000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>2187000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-1136000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2830,12 +3365,13 @@
       </c>
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n">
         <v>-1185000</v>
       </c>
-      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2843,14 +3379,17 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>4857000</v>
+      </c>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
         <v>1136000</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="H42" s="3" t="n">
         <v>7072000</v>
       </c>
     </row>
@@ -2860,18 +3399,19 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
         <v>-916000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>821000</v>
       </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
         <v>2187000</v>
       </c>
-      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2880,21 +3420,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-30296000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-105350000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-54492000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-22118000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-47032000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-39634000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2903,21 +3444,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>60402000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>126105000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>58397000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>27143000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>55245000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>44397000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2926,21 +3468,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>15223000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>109918000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-10957000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-29797000</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>10688000</v>
-      </c>
       <c r="F46" s="3" t="n">
-        <v>805000</v>
+        <v>22355000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2952,10 +3495,11 @@
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
         <v>5016000</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="H47" s="3" t="n">
         <v>2841000</v>
       </c>
     </row>
@@ -2966,21 +3510,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>45179000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>16187000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>69354000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>56940000</v>
       </c>
-      <c r="E48" s="3" t="n">
-        <v>44557000</v>
-      </c>
       <c r="F48" s="3" t="n">
-        <v>38576000</v>
+        <v>32890000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2992,10 +3537,11 @@
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
         <v>2870000</v>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="H49" s="3" t="n">
         <v>3151000</v>
       </c>
     </row>
@@ -3005,16 +3551,19 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
+      <c r="B50" s="3" t="n">
+        <v>45179000</v>
+      </c>
       <c r="C50" s="3" t="n"/>
       <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n">
-        <v>44557000</v>
-      </c>
+      <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n">
+        <v>32890000</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v>35706000</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="H50" s="3" t="n">
         <v>34356000</v>
       </c>
     </row>
@@ -3024,16 +3573,19 @@
           <t>Other Gand A</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
+      <c r="B51" s="3" t="n">
+        <v>45179000</v>
+      </c>
       <c r="C51" s="3" t="n"/>
       <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n">
-        <v>44557000</v>
-      </c>
+      <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n">
+        <v>32890000</v>
+      </c>
+      <c r="G51" s="3" t="n">
         <v>35706000</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="H51" s="3" t="n">
         <v>34356000</v>
       </c>
     </row>
@@ -3044,21 +3596,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>30106000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>20755000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>3905000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>5025000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>8213000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>4763000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3067,21 +3620,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>85138000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>59008000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>77198000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>73603000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>71312000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>90162000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3090,21 +3644,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>115244000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>79763000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>81103000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>78628000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>79525000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>94925000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3113,28 +3668,29 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>115244000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>79763000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>81103000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>78628000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>79525000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>94925000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4598,7 +5154,1463 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>316949000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>314231000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>308381000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>303146000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>299087000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>316949000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>314231000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>308381000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>303146000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>299087000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1050447000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>748947000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>605564000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>476351000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>390115000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2055595000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1162523000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1161229000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1160910000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1194153000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-1305686000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-962740000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-1127960000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-1064676000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-181507000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>749909000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>97585000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-68953000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-6980000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>906550000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1206951000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>114136000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>391170000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>442038000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>637668000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-1305686000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-962740000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-1127960000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-1064676000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-181507000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n">
+        <v>102198000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>102222000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>103214000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>106096000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>109489000</v>
+      </c>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-1305686000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-962740000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-1127960000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-1064676000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-181507000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-244035000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>97585000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-68953000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-6980000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>890336000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-1305686000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-962740000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-1127960000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-1064676000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-181507000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-1305686000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-962740000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-1127960000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-1064676000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-181507000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-4493891000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-4146703000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-4237984000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-4091324000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-3154525000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3188202000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>3183960000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3110021000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>3026645000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2973015000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4375250000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3310384000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3423940000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3042728000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1806878000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1713467000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2528983000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2754077000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2480006000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1611368000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>100649000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>14406000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>13370000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>13391000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>22670000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>116495000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>936107000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1330483000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1316690000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>421902000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>434672000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>428290000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>260348000</v>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>434672000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>428290000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>260348000</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1061651000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1150180000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1149876000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1149925000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1166796000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>89855000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>90869000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>92229000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>94953000</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>97846000</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1061651000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1060325000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1059007000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1057696000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1071843000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2661783000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>781401000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>669863000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>562722000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>195510000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>864948000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3434000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4322000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5914000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5461000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>219555000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>127561000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>83739000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>150127000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>60872000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>219555000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>127561000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>83739000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>150127000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>60872000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>993944000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>12343000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>11353000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>10985000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>27357000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>12343000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>11353000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>10985000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>11143000</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>11643000</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>993944000</v>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n">
+        <v>16214000</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>16290000</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>17941000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>993944000</v>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n">
+        <v>16214000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>16290000</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>17941000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>583336000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>638063000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>570449000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>395696000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>101820000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>364479000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>511957000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>358270000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>180641000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>95492000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>218857000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>126106000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>212179000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>215055000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>6328000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>218857000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>126106000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>212179000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>215055000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>6328000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>3069564000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2347644000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2295980000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1978052000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1625371000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1614732000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1452107000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1234947000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>973292000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>792193000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>163822000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>48481000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>48360000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>36105000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>30699000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1450910000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1403626000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1186587000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>937187000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>761494000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-372193000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>-406893000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-415047000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-403050000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-407184000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>1823103000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1810519000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1601634000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1340237000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1168678000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>925294000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>911066000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>688694000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>477505000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>276764000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>213179000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>190685000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>193341000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>190968000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>196401000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>295367000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>278222000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>279530000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>247266000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>256324000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>74906000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>21769000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>49221000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>28180000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>25151000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>314357000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>408777000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>390848000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>396318000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>414038000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>1454832000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>895537000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1061033000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1004760000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>833178000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>73773000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>247001000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>607590000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>423415000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>133435000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>60244000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>783000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>315667000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>337158000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>1018000</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>7442000</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>6244000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>315667000</v>
+      </c>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>337158000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n">
+        <v>1018000</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>7442000</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>6244000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1005148000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>311378000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>453443000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>581345000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>697942000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1005148000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>311378000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>453443000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>581345000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>697942000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5892,13 +7904,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5908,6 +7920,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5918,30 +7931,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5954,21 +7972,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-139404000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-121789000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-112712000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-87243000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-129057000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-15184000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5977,21 +7996,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>-1095000</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>-547000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-5274000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-4464000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-13641000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6000,7 +8020,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>995000000</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -6012,9 +8032,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>612685000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6022,9 +8043,7 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
@@ -6037,7 +8056,10 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6046,21 +8068,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-389281000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-274857000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-244493000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-121243000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-84016000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-28989000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6069,21 +8092,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-6905000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-57000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>6872000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>564000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>7822000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>2623000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6091,20 +8115,21 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
         <v>-93000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>-159000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>456000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6113,21 +8138,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1145985000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>311378000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>453443000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>581345000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>698725000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>836980000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6136,21 +8162,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>311378000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>453443000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>581345000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>698725000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>836980000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>253802000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6159,21 +8186,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>834607000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-142065000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-127902000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-117380000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-138255000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>583178000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6182,21 +8210,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>971382000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-21808000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-5324000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-31772000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-4198000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>598171000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6205,21 +8234,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>971382000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-21808000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-5324000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-31772000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-4198000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>598171000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6228,17 +8258,20 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-22604000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-26973000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-5893000</v>
       </c>
-      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
         <v>-3845000</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6249,21 +8282,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>5165000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1116000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>364000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>266000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>2972000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6271,9 +8305,7 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
@@ -6286,7 +8318,10 @@
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6294,9 +8329,7 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n">
         <v>0</v>
       </c>
@@ -6309,7 +8342,10 @@
       <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6318,21 +8354,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>993905000</v>
       </c>
       <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>-547000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-5274000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-4464000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>599044000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6341,21 +8378,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>993905000</v>
       </c>
       <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>-547000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-5274000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-4464000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>599044000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6364,21 +8402,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0</v>
+        <v>-1095000</v>
       </c>
       <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>-547000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-5274000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-4464000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-13641000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6387,7 +8426,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>995000000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -6399,9 +8438,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>612685000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6410,21 +8450,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-386652000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-273325000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-254359000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-119608000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-89016000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-28798000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6433,21 +8474,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-386652000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-273325000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-254359000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-119608000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-89016000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-28798000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6456,13 +8498,14 @@
         </is>
       </c>
       <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
         <v>-10124000</v>
       </c>
-      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n">
         <v>-66000</v>
       </c>
     </row>
@@ -6475,11 +8518,12 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6490,11 +8534,12 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6512,10 +8557,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6533,10 +8581,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6545,21 +8596,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-51000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-10124000</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>-36000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-231000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6568,21 +8620,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-51000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-10124000</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>-36000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-231000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6591,21 +8644,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-386597000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-273274000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-244235000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-119608000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-83980000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-28758000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6614,15 +8668,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>2629000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>1532000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>258000</v>
       </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
+        <v>1671000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6631,21 +8692,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-389226000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-274806000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-244493000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-121279000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-83980000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-28758000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6654,21 +8716,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>249877000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>153068000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>131781000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-45041000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>13805000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6677,21 +8740,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>249877000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>153068000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>131781000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-45041000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>13805000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6700,21 +8764,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>62199000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>189004000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>218798000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>100136000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>16595000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-306618000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6723,21 +8788,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>62579000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>205848000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>189156000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>81283000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>38641000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-3980000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6746,13 +8812,14 @@
         </is>
       </c>
       <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
         <v>67932000</v>
       </c>
     </row>
@@ -6763,21 +8830,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-10487000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-13939000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>33492000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-14588000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-11583000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>46121000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6786,21 +8854,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-16361000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-42339000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>34731000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-12504000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>2712000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>46753000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6809,21 +8878,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>5874000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>28400000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-1239000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-2084000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-14295000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-632000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6832,21 +8902,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>5874000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>28400000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-1239000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-2084000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-14295000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-632000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6854,16 +8925,19 @@
           <t>Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>10107000</v>
+      </c>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n">
-        <v>-10469000</v>
-      </c>
+      <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n">
+        <v>-10463000</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>-23080000</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="H43" s="3" t="n">
         <v>-2967000</v>
       </c>
     </row>
@@ -6873,22 +8947,23 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
         <v>-19128000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-3850000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>22972000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="G44" s="3" t="n">
         <v>5221000</v>
       </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6896,22 +8971,23 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
         <v>-19128000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-3850000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>22972000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>5221000</v>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6920,21 +8996,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>178769000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>21450000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-87159000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-74417000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-52893000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>305258000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6943,21 +9020,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>17761000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>27935000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>29946000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>24170000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>16185000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>23967000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6965,18 +9043,23 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="B48" s="3" t="n">
+        <v>266488000</v>
+      </c>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6985,21 +9068,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>19817000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>17115000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>19173000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>21484000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>22407000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>29155000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7008,21 +9092,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>19817000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>17115000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>19173000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>21484000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>22407000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>29155000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7031,21 +9116,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>19817000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>17115000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>19173000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>21484000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>22407000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>29155000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7054,21 +9140,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>52031000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>-327945000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>95050000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>899426000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>-623586000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>227584000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7077,21 +9164,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>38393000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>-331076000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>94750000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>893883000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>-623592000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>227435000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7100,21 +9188,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>13638000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>2575000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>4166000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>149000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7123,34 +9212,35 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>-347188000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>214150000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>-144027000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>-936799000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>576251000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>-265541000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7193,6 +9283,18 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GAAP (statement) ~17% vs yfinance info.grossMargins 22% — info is a non-GAAP basis; FY Summary uses GAAP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
